--- a/output/laminas_comunales/comunal_i_ingr_a_2021_biobio.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2021_biobio.xlsx
@@ -1035,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1044,290 +1044,201 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>615308.3100000001</v>
+          <t>Cañete</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Antuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>926249.8100000001</v>
+          <t>Contulmo</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arauco</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>871540.9399999999</v>
+          <t>Curanilahue</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cabrero</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>763875.5600000001</v>
+          <t>Lebu</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cañete</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>723718.12</v>
+          <t>Los Alamos</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>957074.5</v>
+          <t>Laja</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1019256.75</v>
+          <t>Los Angeles</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Contulmo</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>692688.0600000001</v>
+          <t>Mulchén</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coronel</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>786042.75</v>
+          <t>Nacimiento</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>694863.88</v>
+          <t>Negrete</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>704398.8100000001</v>
+          <t>Quilaco</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualpén</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>839178.6899999999</v>
+          <t>Quilleco</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hualqui</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>709501.62</v>
+          <t>San Rosendo</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laja</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>897477</v>
+          <t>Tucapel</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lebu</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>703340.5600000001</v>
+          <t>Chiguayante</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>701920.0600000001</v>
+          <t>Concepción</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>843906.9399999999</v>
+          <t>Coronel</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lota</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>677551.25</v>
+          <t>Florida</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mulchén</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>674896</v>
+          <t>Hualqui</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>839545.88</v>
+          <t>Lota</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Negrete</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>709605.1899999999</v>
+          <t>San Pedro de la Paz</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Penco</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>774042.0600000001</v>
+          <t>Santa Juana</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quilaco</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>667400.6899999999</v>
+          <t>Yumbel</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quilleco</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>697973.12</v>
+          <t>Cabrero</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>1073287.12</v>
+          <t>Antuco</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>831197.4399999999</v>
+          <t>Alto Biobío</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>693138.5</v>
+          <t>Tirúa</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>733014.1899999999</v>
+          <t>Hualpén</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1336,18 +1247,12 @@
           <t>Talcahuano</t>
         </is>
       </c>
-      <c r="B30">
-        <v>895352.75</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tirúa</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>621487.5600000001</v>
+          <t>Penco</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1356,28 +1261,19 @@
           <t>Tomé</t>
         </is>
       </c>
-      <c r="B32">
-        <v>771031.4399999999</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tucapel</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>739053.75</v>
+          <t>Arauco</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yumbel</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>727869.0600000001</v>
+          <t>Santa Bárbara</t>
+        </is>
       </c>
     </row>
   </sheetData>
